--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488269_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488269_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2754</v>
+        <v>4.9608</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1023</v>
+        <v>1.157</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1731</v>
+        <v>3.8038</v>
       </c>
       <c r="G2" t="n">
         <v>3.5345</v>
@@ -610,13 +610,13 @@
         <v>1.8529</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8145</v>
+        <v>0.4999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1679</v>
+        <v>-0.1131</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.613</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1005</v>
+        <v>2.2488</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3643</v>
+        <v>3.2664</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2638</v>
+        <v>-1.0176</v>
       </c>
       <c r="G3" t="n">
         <v>1.9459</v>
@@ -688,13 +688,13 @@
         <v>0.9264</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.143</v>
+        <v>0.0053</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3457</v>
+        <v>0.2478</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4887</v>
+        <v>-0.2425</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6289</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. LAGHRIDAT</t>
+          <t>T. LUCERO BARBEITO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0698</v>
+        <v>1.9245</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6085</v>
+        <v>1.1762</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4613</v>
+        <v>0.7483</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1658</v>
+        <v>0.8484</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2397</v>
+        <v>1.1235</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07389999999999999</v>
+        <v>-0.2751</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0288</v>
+        <v>0.6158</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8629</v>
+        <v>1.2366</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1659</v>
+        <v>-0.6208</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1945</v>
+        <v>0.2326</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1026</v>
+        <v>-0.1131</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.092</v>
+        <v>0.3457</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3706</v>
+        <v>1.4823</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>1.4823</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2906</v>
+        <v>0.2232</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4326</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.858</v>
+        <v>0.2922</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3155</v>
+        <v>-0.6294</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3155</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4668</v>
+        <v>1.0565</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.631</v>
+        <v>-1.0659</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0978</v>
+        <v>2.1224</v>
       </c>
       <c r="G5" t="n">
         <v>2.3893</v>
@@ -844,13 +844,13 @@
         <v>2.4087</v>
       </c>
       <c r="S5" t="n">
-        <v>1.301</v>
+        <v>0.8907</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9949</v>
+        <v>0.5599</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3061</v>
+        <v>0.3308</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. LUCERO BARBEITO</t>
+          <t>S. LAGHRIDAT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9922</v>
+        <v>0.8918</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5886</v>
+        <v>-0.077</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4036</v>
+        <v>0.9689</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8484</v>
+        <v>-0.1658</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1235</v>
+        <v>-0.2397</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2751</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6158</v>
+        <v>1.0288</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2366</v>
+        <v>0.8629</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6208</v>
+        <v>0.1659</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2326</v>
+        <v>-1.1945</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1131</v>
+        <v>-1.1026</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3457</v>
+        <v>-0.092</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4823</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R6" t="n">
         <v>1.4823</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7091</v>
+        <v>1.1127</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6566</v>
+        <v>0.7471</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0525</v>
+        <v>0.3656</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6294</v>
+        <v>0.3155</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2589</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.271</v>
+        <v>0.1972</v>
       </c>
       <c r="E7" t="n">
         <v>0.0297</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2413</v>
+        <v>0.1675</v>
       </c>
       <c r="G7" t="n">
         <v>0.0467</v>
@@ -1000,13 +1000,13 @@
         <v>0.1853</v>
       </c>
       <c r="S7" t="n">
-        <v>0.039</v>
+        <v>-0.0348</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0547</v>
       </c>
       <c r="U7" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.0199</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2233</v>
+        <v>-1.149</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1067</v>
+        <v>-1.8354</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8834</v>
+        <v>0.6865</v>
       </c>
       <c r="G8" t="n">
         <v>1.0724</v>
@@ -1078,13 +1078,13 @@
         <v>1.4823</v>
       </c>
       <c r="S8" t="n">
-        <v>1.8733</v>
+        <v>0.9476</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3779</v>
+        <v>0.6491</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4954</v>
+        <v>0.2984</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9455</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9403</v>
+        <v>-1.3276</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8637</v>
+        <v>-1.3741</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0766</v>
+        <v>0.0465</v>
       </c>
       <c r="G9" t="n">
         <v>0.8337</v>
@@ -1156,13 +1156,13 @@
         <v>2.2234</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9414</v>
+        <v>-0.3286</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7113</v>
+        <v>-0.2216</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2301</v>
+        <v>-0.107</v>
       </c>
       <c r="V9" t="n">
         <v>-2.2033</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1048</v>
+        <v>-1.4127</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3701</v>
+        <v>-1.8258</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2654</v>
+        <v>0.4131</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1674</v>
@@ -1234,13 +1234,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5668</v>
+        <v>0.1253</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3283</v>
+        <v>0.2161</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2385</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3281</v>
+        <v>-2.5375</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0715</v>
+        <v>-1.5272</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2565</v>
+        <v>-1.0103</v>
       </c>
       <c r="G11" t="n">
         <v>0.0622</v>
@@ -1312,13 +1312,13 @@
         <v>1.297</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6317</v>
+        <v>0.1589</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4166</v>
+        <v>0.1278</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2151</v>
+        <v>0.0311</v>
       </c>
       <c r="V11" t="n">
         <v>-2.2027</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.5792</v>
+        <v>4.8528</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3496</v>
+        <v>-2.0761</v>
       </c>
       <c r="F12" t="n">
-        <v>6.928999999999999</v>
+        <v>6.929100000000001</v>
       </c>
       <c r="G12" t="n">
         <v>9.399899999999999</v>
@@ -1369,7 +1369,7 @@
         <v>10.605</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03719999999999998</v>
+        <v>0.03720000000000021</v>
       </c>
       <c r="M12" t="n">
         <v>-1.2419</v>
@@ -1390,13 +1390,13 @@
         <v>13.8965</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3264</v>
+        <v>3.6002</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8157</v>
+        <v>2.0894</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5108</v>
+        <v>1.5107</v>
       </c>
       <c r="V12" t="n">
         <v>-6.2943</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.1794</v>
+        <v>2.7257</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0636</v>
+        <v>1.5532</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1158</v>
+        <v>1.1725</v>
       </c>
       <c r="G13" t="n">
         <v>-0.9677</v>
@@ -1468,13 +1468,13 @@
         <v>2.0382</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0938</v>
+        <v>-0.5475</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8207</v>
+        <v>-0.3311</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2731</v>
+        <v>-0.2164</v>
       </c>
       <c r="V13" t="n">
         <v>2.2027</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K. DELGADO YEBOAH</t>
+          <t>J. REYES BARRANCO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.887</v>
+        <v>1.4196</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4545</v>
+        <v>1.995</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3415</v>
+        <v>-0.5754</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.7543</v>
+        <v>2.819</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.0033</v>
+        <v>0.1004</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.751</v>
+        <v>2.7186</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.5772</v>
+        <v>4.4573</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3959</v>
+        <v>1.8848</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.1813</v>
+        <v>2.5725</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1771</v>
+        <v>-1.6382</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.6074</v>
+        <v>-1.7844</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4303</v>
+        <v>0.1462</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.7793</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9646</v>
+        <v>2.7793</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4347</v>
+        <v>-0.7694</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7549</v>
+        <v>-0.3118</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3201</v>
+        <v>-0.4576</v>
       </c>
       <c r="V14" t="n">
-        <v>3.0212</v>
+        <v>-0.63</v>
       </c>
       <c r="W14" t="n">
-        <v>3.1471</v>
+        <v>0.6289</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1259</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. REYES BARRANCO</t>
+          <t>K. DELGADO YEBOAH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8475</v>
+        <v>0.2828</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7012</v>
+        <v>-1.14</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8537</v>
+        <v>1.4228</v>
       </c>
       <c r="G15" t="n">
-        <v>2.819</v>
+        <v>-2.7543</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1004</v>
+        <v>-2.0033</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7186</v>
+        <v>-0.751</v>
       </c>
       <c r="J15" t="n">
-        <v>4.4573</v>
+        <v>-1.5772</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8848</v>
+        <v>-0.3959</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5725</v>
+        <v>-1.1813</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6382</v>
+        <v>-1.1771</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.7844</v>
+        <v>-1.6074</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1462</v>
+        <v>0.4303</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.7793</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7793</v>
+        <v>2.9646</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3415</v>
+        <v>-0.1694</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6056</v>
+        <v>0.0694</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7359</v>
+        <v>-0.2388</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.63</v>
+        <v>3.0212</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6289</v>
+        <v>3.1471</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2589</v>
+        <v>-0.1259</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. KOZAR SIMIONIKA</t>
+          <t>S. TRUJILLO SUAREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6045</v>
+        <v>-0.653</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.3221</v>
+        <v>-0.7956</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7176</v>
+        <v>0.1426</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0104</v>
+        <v>-2.3951</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3435</v>
+        <v>-1.5796</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-0.8155</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1005</v>
+        <v>-1.0557</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7213000000000001</v>
+        <v>-0.4858</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6208</v>
+        <v>-0.5699</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1108</v>
+        <v>-1.3394</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0648</v>
+        <v>-1.0938</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.046</v>
+        <v>-0.2456</v>
       </c>
       <c r="P16" t="n">
+        <v>0.7411</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-0.9264</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-2.7793</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.8529</v>
+        <v>1.6676</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3323</v>
+        <v>-0.4464</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3567</v>
+        <v>-0.3867</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0244</v>
+        <v>-0.0597</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.4474</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1259</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. TRUJILLO SUAREZ</t>
+          <t>O. FAJANA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6851</v>
+        <v>-1.129</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7956</v>
+        <v>-2.0207</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1105</v>
+        <v>0.8917</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.3951</v>
+        <v>-0.599</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5796</v>
+        <v>-1.5836</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8155</v>
+        <v>0.9846</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.0557</v>
+        <v>0.8479</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4858</v>
+        <v>0.163</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5699</v>
+        <v>0.6849</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3394</v>
+        <v>-1.447</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0938</v>
+        <v>-1.7467</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2456</v>
+        <v>0.2997</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7411</v>
+        <v>0.1853</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6676</v>
+        <v>2.0382</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4785</v>
+        <v>-0.9044</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3867</v>
+        <v>-0.3858</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4474</v>
+        <v>0.1891</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5733</v>
+        <v>-0.63</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1259</v>
+        <v>0.8191000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. FAJANA</t>
+          <t>M. KOZAR SIMIONIKA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9462</v>
+        <v>-1.6576</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5103</v>
+        <v>-2.3014</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5642</v>
+        <v>0.6438</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.599</v>
+        <v>-1.0104</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5836</v>
+        <v>-0.3435</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9846</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8479</v>
+        <v>0.1005</v>
       </c>
       <c r="K18" t="n">
-        <v>0.163</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6849</v>
+        <v>-0.6208</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.447</v>
+        <v>-1.1108</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7467</v>
+        <v>-1.0648</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2997</v>
+        <v>-0.046</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1853</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8529</v>
+        <v>-2.7793</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0382</v>
+        <v>1.8529</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.7216</v>
+        <v>0.2792</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8754</v>
+        <v>0.3774</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8461</v>
+        <v>-0.0982</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1891</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.8191000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5922</v>
+        <v>-2.2984</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.499</v>
+        <v>-1.2052</v>
       </c>
       <c r="F19" t="n">
         <v>-1.0932</v>
@@ -1936,10 +1936,10 @@
         <v>0.3706</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3159</v>
+        <v>-0.0221</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6566</v>
+        <v>-0.3628</v>
       </c>
       <c r="U19" t="n">
         <v>0.3407</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6653</v>
+        <v>-2.6166</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1122</v>
+        <v>-3.0143</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4469</v>
+        <v>0.3976</v>
       </c>
       <c r="G20" t="n">
         <v>-2.286</v>
@@ -2014,13 +2014,13 @@
         <v>2.0382</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1423</v>
+        <v>-0.0936</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2773</v>
+        <v>-0.1794</v>
       </c>
       <c r="U20" t="n">
-        <v>0.135</v>
+        <v>0.0858</v>
       </c>
       <c r="V20" t="n">
         <v>0.5041</v>
@@ -2047,28 +2047,28 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5794</v>
+        <v>-3.9265</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.9289</v>
+        <v>-6.929</v>
       </c>
       <c r="F21" t="n">
-        <v>2.349600000000001</v>
+        <v>3.0024</v>
       </c>
       <c r="G21" t="n">
-        <v>-9.4001</v>
+        <v>-9.400099999999998</v>
       </c>
       <c r="H21" t="n">
         <v>-8.632099999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7678999999999998</v>
+        <v>-0.7679</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2419</v>
+        <v>1.241899999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>1.9726</v>
+        <v>1.972600000000001</v>
       </c>
       <c r="L21" t="n">
         <v>-0.7307000000000001</v>
@@ -2092,22 +2092,22 @@
         <v>15.7496</v>
       </c>
       <c r="S21" t="n">
-        <v>-3.3266</v>
+        <v>-2.6736</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.5107</v>
+        <v>-1.5108</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.8157</v>
+        <v>-1.1628</v>
       </c>
       <c r="V21" t="n">
-        <v>6.2942</v>
+        <v>6.294200000000001</v>
       </c>
       <c r="W21" t="n">
         <v>7.2364</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.9422999999999998</v>
+        <v>-0.9422999999999999</v>
       </c>
     </row>
   </sheetData>
